--- a/Список проверенных переводов.xlsx
+++ b/Список проверенных переводов.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danil\OneDrive\Рабочий стол\СЦЕНАРИИ\Незакончено\DBD_Trans-master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41228AB3-D2FF-4DA9-B406-010EE45D41A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4B9973-95F8-4637-B74B-16DAFE6B7D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="102">
   <si>
     <t>Траппер</t>
   </si>
@@ -335,16 +335,13 @@
   </si>
   <si>
     <t>нет</t>
-  </si>
-  <si>
-    <t>ы</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -374,6 +371,15 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -421,7 +427,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -440,9 +446,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -456,6 +459,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -758,52 +767,52 @@
       <c r="E1" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="B2" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="B3" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="12" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -823,7 +832,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -843,22 +852,22 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="B6" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>44</v>
       </c>
     </row>
@@ -883,7 +892,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="12" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -923,7 +932,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="12" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -983,22 +992,22 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="2" t="s">
+      <c r="B13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="8" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1063,7 +1072,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="12" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -1083,22 +1092,22 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="9" t="s">
+      <c r="B18" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="E18" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F18" s="9" t="s">
+      <c r="E18" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1141,9 +1150,7 @@
       <c r="F20" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H20" s="12" t="s">
-        <v>102</v>
-      </c>
+      <c r="H20" s="11"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
@@ -1206,142 +1213,142 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="9" t="s">
+      <c r="B24" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>43</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E24" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F24" s="9" t="s">
+      <c r="E24" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" s="8" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="9" t="s">
+      <c r="B25" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="E25" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F25" s="9" t="s">
+      <c r="E25" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" s="8" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="9" t="s">
+      <c r="B26" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="E26" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F26" s="9" t="s">
+      <c r="E26" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="8" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" s="2" t="s">
+      <c r="B27" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F28" s="2" t="s">
+      <c r="B28" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F29" s="2" t="s">
+      <c r="B29" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" s="9" t="s">
+      <c r="B30" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="E30" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F30" s="9" t="s">
+      <c r="E30" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" s="8" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1406,27 +1413,27 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F34" s="2" t="s">
+      <c r="B34" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F34" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="12" t="s">
         <v>32</v>
       </c>
       <c r="B35" s="2" t="s">
@@ -1446,7 +1453,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="12" t="s">
         <v>33</v>
       </c>
       <c r="B36" s="2" t="s">
@@ -1466,22 +1473,22 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F37" s="2" t="s">
+      <c r="B37" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F37" s="8" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1526,82 +1533,82 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F40" s="2" t="s">
+      <c r="B40" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F40" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F41" s="2" t="s">
+      <c r="B41" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F41" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F42" s="2" t="s">
+      <c r="B42" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F42" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
+      <c r="A43" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F43" s="2" t="s">
+      <c r="B43" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F43" s="8" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1634,7 +1641,7 @@
       <c r="E1" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>99</v>
       </c>
     </row>
@@ -2619,7 +2626,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="7" t="s">
         <v>97</v>
       </c>
       <c r="B51" s="2" t="s">
@@ -2639,7 +2646,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="7" t="s">
         <v>98</v>
       </c>
       <c r="B52" s="2" t="s">
@@ -2659,7 +2666,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="7" t="s">
         <v>100</v>
       </c>
       <c r="B53" s="1"/>

--- a/Список проверенных переводов.xlsx
+++ b/Список проверенных переводов.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danil\OneDrive\Рабочий стол\СЦЕНАРИИ\Незакончено\DBD_Trans-master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4B9973-95F8-4637-B74B-16DAFE6B7D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6EDCA18-6C1B-4470-BC14-FACD730B6927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -872,7 +872,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="12" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -1513,7 +1513,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="12" t="s">
         <v>36</v>
       </c>
       <c r="B39" s="2" t="s">

--- a/Список проверенных переводов.xlsx
+++ b/Список проверенных переводов.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danil\OneDrive\Рабочий стол\СЦЕНАРИИ\Незакончено\DBD_Trans-master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6EDCA18-6C1B-4470-BC14-FACD730B6927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{351F2A10-3C59-4CF2-8704-BC9FB89F9203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -912,7 +912,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="12" t="s">
         <v>94</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -952,7 +952,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -972,7 +972,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="10" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -1012,7 +1012,7 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -1112,7 +1112,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="12" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -1153,7 +1153,7 @@
       <c r="H20" s="11"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="12" t="s">
         <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -1493,7 +1493,7 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="12" t="s">
         <v>35</v>
       </c>
       <c r="B38" s="2" t="s">

--- a/Список проверенных переводов.xlsx
+++ b/Список проверенных переводов.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danil\OneDrive\Рабочий стол\СЦЕНАРИИ\Незакончено\DBD_Trans-master\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Disposable\Desktop\СЦЕНАРИИ\В процессе\DanilChem\DBD_Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6EDCA18-6C1B-4470-BC14-FACD730B6927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F767DF-052B-4B09-9E1E-ED3A80343B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Маньяки" sheetId="1" r:id="rId1"/>
@@ -20,9 +20,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -427,7 +424,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -445,25 +442,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -747,13 +735,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="5" t="s">
         <v>40</v>
@@ -767,52 +755,52 @@
       <c r="E1" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="B2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="B3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -831,8 +819,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -851,28 +839,28 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="B6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -891,8 +879,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -911,8 +899,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
         <v>94</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -931,8 +919,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -951,8 +939,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -971,8 +959,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -991,27 +979,27 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>11</v>
       </c>
@@ -1031,7 +1019,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>12</v>
       </c>
@@ -1051,7 +1039,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>13</v>
       </c>
@@ -1071,8 +1059,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -1091,27 +1079,27 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="8" t="s">
+      <c r="B18" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E18" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E18" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>16</v>
       </c>
@@ -1131,7 +1119,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>17</v>
       </c>
@@ -1150,10 +1138,10 @@
       <c r="F20" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H20" s="11"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+      <c r="H20" s="9"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="10" t="s">
         <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -1172,7 +1160,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>19</v>
       </c>
@@ -1192,7 +1180,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>20</v>
       </c>
@@ -1212,147 +1200,147 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="8" t="s">
+      <c r="B24" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>43</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E24" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
+      <c r="E24" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="8" t="s">
+      <c r="B25" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E25" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
+      <c r="E25" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="8" t="s">
+      <c r="B26" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E26" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
+      <c r="E26" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
+      <c r="B27" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
+      <c r="B28" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
+      <c r="B29" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" s="8" t="s">
+      <c r="B30" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E30" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E30" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>28</v>
       </c>
@@ -1372,7 +1360,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>29</v>
       </c>
@@ -1392,7 +1380,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>30</v>
       </c>
@@ -1412,28 +1400,28 @@
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="10" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B34" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
+      <c r="B34" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="10" t="s">
         <v>32</v>
       </c>
       <c r="B35" s="2" t="s">
@@ -1452,8 +1440,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="10" t="s">
         <v>33</v>
       </c>
       <c r="B36" s="2" t="s">
@@ -1472,28 +1460,28 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="10" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
+      <c r="B37" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B38" s="2" t="s">
@@ -1512,8 +1500,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="10" t="s">
         <v>36</v>
       </c>
       <c r="B39" s="2" t="s">
@@ -1532,83 +1520,83 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B40" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
+      <c r="B40" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
+      <c r="B41" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B42" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="13" t="s">
+      <c r="B42" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="B43" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F43" s="8" t="s">
+      <c r="B43" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F43" s="7" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1621,13 +1609,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F14EA754-DAC8-467E-93D7-CE1BA44B51C5}">
   <dimension ref="A1:F53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
         <v>40</v>
@@ -1641,11 +1629,11 @@
       <c r="E1" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>45</v>
       </c>
@@ -1665,7 +1653,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>46</v>
       </c>
@@ -1685,7 +1673,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>47</v>
       </c>
@@ -1705,7 +1693,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>48</v>
       </c>
@@ -1725,7 +1713,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>49</v>
       </c>
@@ -1745,7 +1733,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>50</v>
       </c>
@@ -1765,7 +1753,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>51</v>
       </c>
@@ -1785,7 +1773,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>52</v>
       </c>
@@ -1805,7 +1793,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>66</v>
       </c>
@@ -1825,7 +1813,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>53</v>
       </c>
@@ -1845,7 +1833,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>54</v>
       </c>
@@ -1865,7 +1853,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>55</v>
       </c>
@@ -1885,7 +1873,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>56</v>
       </c>
@@ -1905,7 +1893,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>57</v>
       </c>
@@ -1925,7 +1913,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>58</v>
       </c>
@@ -1945,7 +1933,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>59</v>
       </c>
@@ -1965,7 +1953,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>67</v>
       </c>
@@ -1985,7 +1973,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>60</v>
       </c>
@@ -2005,7 +1993,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>61</v>
       </c>
@@ -2025,7 +2013,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>62</v>
       </c>
@@ -2045,7 +2033,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>63</v>
       </c>
@@ -2065,7 +2053,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>64</v>
       </c>
@@ -2085,7 +2073,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>65</v>
       </c>
@@ -2105,7 +2093,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>68</v>
       </c>
@@ -2125,7 +2113,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>69</v>
       </c>
@@ -2145,7 +2133,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>70</v>
       </c>
@@ -2165,7 +2153,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>71</v>
       </c>
@@ -2185,7 +2173,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>83</v>
       </c>
@@ -2205,7 +2193,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>72</v>
       </c>
@@ -2225,7 +2213,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>73</v>
       </c>
@@ -2245,7 +2233,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>74</v>
       </c>
@@ -2265,7 +2253,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>75</v>
       </c>
@@ -2285,7 +2273,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>76</v>
       </c>
@@ -2305,7 +2293,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>77</v>
       </c>
@@ -2325,7 +2313,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>78</v>
       </c>
@@ -2345,7 +2333,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>79</v>
       </c>
@@ -2365,7 +2353,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>80</v>
       </c>
@@ -2385,7 +2373,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>81</v>
       </c>
@@ -2405,7 +2393,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>82</v>
       </c>
@@ -2425,7 +2413,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>90</v>
       </c>
@@ -2445,7 +2433,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>84</v>
       </c>
@@ -2465,7 +2453,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>85</v>
       </c>
@@ -2485,7 +2473,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>86</v>
       </c>
@@ -2505,7 +2493,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>87</v>
       </c>
@@ -2525,7 +2513,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>88</v>
       </c>
@@ -2545,7 +2533,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>89</v>
       </c>
@@ -2565,7 +2553,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>91</v>
       </c>
@@ -2585,7 +2573,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>92</v>
       </c>
@@ -2605,7 +2593,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>93</v>
       </c>
@@ -2625,8 +2613,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
         <v>97</v>
       </c>
       <c r="B51" s="2" t="s">
@@ -2645,8 +2633,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="7" t="s">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
         <v>98</v>
       </c>
       <c r="B52" s="2" t="s">
@@ -2665,8 +2653,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
         <v>100</v>
       </c>
       <c r="B53" s="1"/>

--- a/Список проверенных переводов.xlsx
+++ b/Список проверенных переводов.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danil\OneDrive\Рабочий стол\СЦЕНАРИИ\Незакончено\DBD_Trans-master\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Disposable\Desktop\СЦЕНАРИИ\В процессе\DanilChem\DBD_Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{351F2A10-3C59-4CF2-8704-BC9FB89F9203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02532AB1-A322-4B7A-9FDE-754F901452C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Маньяки" sheetId="1" r:id="rId1"/>
@@ -21,15 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="104">
   <si>
     <t>Траппер</t>
   </si>
@@ -335,6 +332,12 @@
   </si>
   <si>
     <t>нет</t>
+  </si>
+  <si>
+    <t>Джейсон</t>
+  </si>
+  <si>
+    <t>Шейн</t>
   </si>
 </sst>
 </file>
@@ -391,7 +394,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -423,6 +426,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -445,27 +472,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -746,14 +769,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H44"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="5" t="s">
         <v>40</v>
@@ -767,52 +790,52 @@
       <c r="E1" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="B2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="B3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -831,8 +854,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -851,28 +874,28 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="B6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -891,8 +914,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -911,8 +934,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
         <v>94</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -931,8 +954,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -951,8 +974,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -971,8 +994,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -991,28 +1014,28 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="B13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -1031,8 +1054,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -1051,8 +1074,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -1071,8 +1094,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -1091,28 +1114,28 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="8" t="s">
+      <c r="B18" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E18" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="E18" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -1131,8 +1154,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="10" t="s">
         <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -1150,10 +1173,10 @@
       <c r="F20" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H20" s="11"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="H20" s="9"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="10" t="s">
         <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -1172,8 +1195,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="10" t="s">
         <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -1192,7 +1215,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>20</v>
       </c>
@@ -1212,147 +1235,147 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="8" t="s">
+      <c r="B24" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>43</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E24" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
+      <c r="E24" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="8" t="s">
+      <c r="B25" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E25" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
+      <c r="E25" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="8" t="s">
+      <c r="B26" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E26" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
+      <c r="E26" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
+      <c r="B27" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
+      <c r="B28" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
+      <c r="B29" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" s="8" t="s">
+      <c r="B30" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E30" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E30" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>28</v>
       </c>
@@ -1372,7 +1395,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>29</v>
       </c>
@@ -1392,7 +1415,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>30</v>
       </c>
@@ -1412,28 +1435,28 @@
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="10" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B34" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
+      <c r="B34" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="10" t="s">
         <v>32</v>
       </c>
       <c r="B35" s="2" t="s">
@@ -1452,8 +1475,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="10" t="s">
         <v>33</v>
       </c>
       <c r="B36" s="2" t="s">
@@ -1472,28 +1495,28 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="10" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
+      <c r="B37" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B38" s="2" t="s">
@@ -1512,8 +1535,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="10" t="s">
         <v>36</v>
       </c>
       <c r="B39" s="2" t="s">
@@ -1532,85 +1555,95 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B40" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
+      <c r="B40" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
+      <c r="B41" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B42" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="13" t="s">
+      <c r="B42" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="B43" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>44</v>
-      </c>
+      <c r="B43" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1620,14 +1653,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F14EA754-DAC8-467E-93D7-CE1BA44B51C5}">
-  <dimension ref="A1:F53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F54"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
         <v>40</v>
@@ -1641,11 +1674,11 @@
       <c r="E1" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>45</v>
       </c>
@@ -1665,7 +1698,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>46</v>
       </c>
@@ -1685,7 +1718,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>47</v>
       </c>
@@ -1705,7 +1738,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>48</v>
       </c>
@@ -1725,7 +1758,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>49</v>
       </c>
@@ -1745,7 +1778,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>50</v>
       </c>
@@ -1765,7 +1798,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>51</v>
       </c>
@@ -1785,7 +1818,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>52</v>
       </c>
@@ -1805,7 +1838,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>66</v>
       </c>
@@ -1825,7 +1858,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>53</v>
       </c>
@@ -1845,7 +1878,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>54</v>
       </c>
@@ -1865,7 +1898,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>55</v>
       </c>
@@ -1885,7 +1918,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>56</v>
       </c>
@@ -1905,7 +1938,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>57</v>
       </c>
@@ -1925,7 +1958,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>58</v>
       </c>
@@ -1945,7 +1978,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>59</v>
       </c>
@@ -1965,7 +1998,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>67</v>
       </c>
@@ -1985,7 +2018,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>60</v>
       </c>
@@ -2005,7 +2038,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>61</v>
       </c>
@@ -2025,7 +2058,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>62</v>
       </c>
@@ -2045,7 +2078,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>63</v>
       </c>
@@ -2065,7 +2098,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>64</v>
       </c>
@@ -2085,7 +2118,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>65</v>
       </c>
@@ -2105,7 +2138,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>68</v>
       </c>
@@ -2125,7 +2158,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>69</v>
       </c>
@@ -2145,7 +2178,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>70</v>
       </c>
@@ -2165,7 +2198,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>71</v>
       </c>
@@ -2185,7 +2218,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>83</v>
       </c>
@@ -2205,7 +2238,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>72</v>
       </c>
@@ -2225,7 +2258,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>73</v>
       </c>
@@ -2245,7 +2278,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>74</v>
       </c>
@@ -2265,7 +2298,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>75</v>
       </c>
@@ -2285,7 +2318,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>76</v>
       </c>
@@ -2305,7 +2338,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>77</v>
       </c>
@@ -2325,7 +2358,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>78</v>
       </c>
@@ -2345,7 +2378,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>79</v>
       </c>
@@ -2365,7 +2398,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>80</v>
       </c>
@@ -2385,7 +2418,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>81</v>
       </c>
@@ -2405,7 +2438,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>82</v>
       </c>
@@ -2425,7 +2458,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>90</v>
       </c>
@@ -2445,7 +2478,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>84</v>
       </c>
@@ -2465,7 +2498,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>85</v>
       </c>
@@ -2485,7 +2518,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>86</v>
       </c>
@@ -2505,7 +2538,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>87</v>
       </c>
@@ -2525,7 +2558,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>88</v>
       </c>
@@ -2545,7 +2578,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>89</v>
       </c>
@@ -2565,7 +2598,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>91</v>
       </c>
@@ -2585,7 +2618,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>92</v>
       </c>
@@ -2605,7 +2638,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>93</v>
       </c>
@@ -2625,8 +2658,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
         <v>97</v>
       </c>
       <c r="B51" s="2" t="s">
@@ -2645,8 +2678,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="7" t="s">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
         <v>98</v>
       </c>
       <c r="B52" s="2" t="s">
@@ -2665,8 +2698,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
         <v>100</v>
       </c>
       <c r="B53" s="1"/>
@@ -2675,6 +2708,16 @@
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
     </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B54" s="12"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="13"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Список проверенных переводов.xlsx
+++ b/Список проверенных переводов.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Disposable\Desktop\СЦЕНАРИИ\В процессе\DanilChem\DBD_Localization\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/842728658d9fcf8d/Рабочий стол/СЦЕНАРИИ/Незакончено/DBD_Trans-master/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02532AB1-A322-4B7A-9FDE-754F901452C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{C43E7977-282A-4B27-9346-D88CA0B656F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98B62A9E-A2FF-4060-A07E-D74DAAF1F0C6}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Маньяки" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -770,13 +773,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="5" t="s">
         <v>40</v>
@@ -794,7 +797,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
@@ -814,7 +817,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
@@ -834,7 +837,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
@@ -854,7 +857,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>3</v>
       </c>
@@ -874,7 +877,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>4</v>
       </c>
@@ -894,7 +897,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>5</v>
       </c>
@@ -914,7 +917,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>6</v>
       </c>
@@ -934,7 +937,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>94</v>
       </c>
@@ -954,7 +957,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>7</v>
       </c>
@@ -974,7 +977,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>8</v>
       </c>
@@ -994,7 +997,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>9</v>
       </c>
@@ -1014,7 +1017,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>10</v>
       </c>
@@ -1034,7 +1037,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>11</v>
       </c>
@@ -1054,7 +1057,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>12</v>
       </c>
@@ -1074,7 +1077,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>13</v>
       </c>
@@ -1094,7 +1097,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>14</v>
       </c>
@@ -1114,7 +1117,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>15</v>
       </c>
@@ -1134,7 +1137,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>16</v>
       </c>
@@ -1154,7 +1157,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>17</v>
       </c>
@@ -1175,7 +1178,7 @@
       </c>
       <c r="H20" s="9"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>18</v>
       </c>
@@ -1195,7 +1198,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>19</v>
       </c>
@@ -1215,8 +1218,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -1235,7 +1238,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>21</v>
       </c>
@@ -1255,7 +1258,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>22</v>
       </c>
@@ -1275,7 +1278,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>23</v>
       </c>
@@ -1295,7 +1298,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>24</v>
       </c>
@@ -1315,7 +1318,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>25</v>
       </c>
@@ -1335,7 +1338,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>26</v>
       </c>
@@ -1355,7 +1358,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>27</v>
       </c>
@@ -1375,8 +1378,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="6" t="s">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
         <v>28</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -1395,7 +1398,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>29</v>
       </c>
@@ -1415,8 +1418,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="6" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="10" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="2" t="s">
@@ -1435,7 +1438,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>31</v>
       </c>
@@ -1455,7 +1458,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>32</v>
       </c>
@@ -1475,7 +1478,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
         <v>33</v>
       </c>
@@ -1495,7 +1498,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
@@ -1515,7 +1518,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
         <v>35</v>
       </c>
@@ -1535,7 +1538,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>36</v>
       </c>
@@ -1555,7 +1558,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
         <v>37</v>
       </c>
@@ -1575,7 +1578,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
         <v>38</v>
       </c>
@@ -1595,7 +1598,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
         <v>39</v>
       </c>
@@ -1615,7 +1618,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
         <v>96</v>
       </c>
@@ -1635,7 +1638,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
         <v>102</v>
       </c>
@@ -1654,13 +1657,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F14EA754-DAC8-467E-93D7-CE1BA44B51C5}">
   <dimension ref="A1:F54"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
         <v>40</v>
@@ -1678,7 +1681,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>45</v>
       </c>
@@ -1698,7 +1701,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>46</v>
       </c>
@@ -1718,7 +1721,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>47</v>
       </c>
@@ -1738,7 +1741,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>48</v>
       </c>
@@ -1758,7 +1761,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>49</v>
       </c>
@@ -1778,7 +1781,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>50</v>
       </c>
@@ -1798,7 +1801,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>51</v>
       </c>
@@ -1818,7 +1821,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>52</v>
       </c>
@@ -1838,7 +1841,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>66</v>
       </c>
@@ -1858,7 +1861,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>53</v>
       </c>
@@ -1878,7 +1881,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>54</v>
       </c>
@@ -1898,7 +1901,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>55</v>
       </c>
@@ -1918,7 +1921,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>56</v>
       </c>
@@ -1938,7 +1941,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>57</v>
       </c>
@@ -1958,7 +1961,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>58</v>
       </c>
@@ -1978,7 +1981,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>59</v>
       </c>
@@ -1998,7 +2001,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>67</v>
       </c>
@@ -2018,7 +2021,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>60</v>
       </c>
@@ -2038,7 +2041,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>61</v>
       </c>
@@ -2058,7 +2061,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>62</v>
       </c>
@@ -2078,7 +2081,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>63</v>
       </c>
@@ -2098,7 +2101,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>64</v>
       </c>
@@ -2118,7 +2121,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>65</v>
       </c>
@@ -2138,7 +2141,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>68</v>
       </c>
@@ -2158,7 +2161,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>69</v>
       </c>
@@ -2178,7 +2181,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>70</v>
       </c>
@@ -2198,7 +2201,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>71</v>
       </c>
@@ -2218,7 +2221,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>83</v>
       </c>
@@ -2238,7 +2241,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>72</v>
       </c>
@@ -2258,7 +2261,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>73</v>
       </c>
@@ -2278,7 +2281,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>74</v>
       </c>
@@ -2298,7 +2301,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>75</v>
       </c>
@@ -2318,7 +2321,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>76</v>
       </c>
@@ -2338,7 +2341,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>77</v>
       </c>
@@ -2358,7 +2361,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>78</v>
       </c>
@@ -2378,7 +2381,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>79</v>
       </c>
@@ -2398,7 +2401,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>80</v>
       </c>
@@ -2418,7 +2421,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>81</v>
       </c>
@@ -2438,7 +2441,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>82</v>
       </c>
@@ -2458,7 +2461,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>90</v>
       </c>
@@ -2478,7 +2481,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>84</v>
       </c>
@@ -2498,7 +2501,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>85</v>
       </c>
@@ -2518,7 +2521,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>86</v>
       </c>
@@ -2538,7 +2541,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>87</v>
       </c>
@@ -2558,7 +2561,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>88</v>
       </c>
@@ -2578,7 +2581,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>89</v>
       </c>
@@ -2598,7 +2601,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>91</v>
       </c>
@@ -2618,7 +2621,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>92</v>
       </c>
@@ -2638,7 +2641,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>93</v>
       </c>
@@ -2658,7 +2661,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>97</v>
       </c>
@@ -2678,7 +2681,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>98</v>
       </c>
@@ -2698,7 +2701,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>100</v>
       </c>
@@ -2708,7 +2711,7 @@
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
         <v>103</v>
       </c>

--- a/Список проверенных переводов.xlsx
+++ b/Список проверенных переводов.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/842728658d9fcf8d/Рабочий стол/СЦЕНАРИИ/Незакончено/DBD_Trans-master/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Disposable\Desktop\СЦЕНАРИИ\В процессе\DanilChem\DBD_Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{C43E7977-282A-4B27-9346-D88CA0B656F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98B62A9E-A2FF-4060-A07E-D74DAAF1F0C6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71C612B6-6801-4F16-ACDA-EF5E9A566EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Маньяки" sheetId="1" r:id="rId1"/>
@@ -20,9 +20,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -472,9 +469,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -492,6 +486,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -773,13 +770,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="5" t="s">
         <v>40</v>
@@ -797,48 +794,48 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="B2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="B3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -857,8 +854,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -877,28 +874,28 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="B6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -917,8 +914,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -937,8 +934,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
         <v>94</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -957,8 +954,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -977,8 +974,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -997,8 +994,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -1017,28 +1014,28 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="B13" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -1057,8 +1054,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -1077,8 +1074,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -1097,8 +1094,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -1117,28 +1114,28 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="7" t="s">
+      <c r="B18" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
+      <c r="E18" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="9" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -1157,8 +1154,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -1176,10 +1173,10 @@
       <c r="F20" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H20" s="9"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
+      <c r="H20" s="8"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="9" t="s">
         <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -1198,8 +1195,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -1218,8 +1215,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="9" t="s">
         <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -1238,148 +1235,148 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="7" t="s">
+      <c r="B24" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>43</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+      <c r="E24" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="7" t="s">
+      <c r="B25" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
+      <c r="E25" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="7" t="s">
+      <c r="B26" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E26" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
+      <c r="E26" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
+      <c r="B27" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
+      <c r="B28" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="s">
+      <c r="B29" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" s="7" t="s">
+      <c r="B30" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E30" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
+      <c r="E30" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="9" t="s">
         <v>28</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -1398,8 +1395,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -1418,8 +1415,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="10" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="2" t="s">
@@ -1438,28 +1435,28 @@
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="10" t="s">
+      <c r="B34" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B35" s="2" t="s">
@@ -1478,8 +1475,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="10" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="9" t="s">
         <v>33</v>
       </c>
       <c r="B36" s="2" t="s">
@@ -1498,28 +1495,28 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
+      <c r="B37" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B38" s="2" t="s">
@@ -1538,8 +1535,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="10" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="9" t="s">
         <v>36</v>
       </c>
       <c r="B39" s="2" t="s">
@@ -1558,88 +1555,88 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="10" t="s">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B40" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="10" t="s">
+      <c r="B40" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="10" t="s">
+      <c r="B41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="10" t="s">
+      <c r="B42" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="B43" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="10" t="s">
+      <c r="B43" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="9" t="s">
         <v>102</v>
       </c>
       <c r="B44" s="1"/>
@@ -1657,13 +1654,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F14EA754-DAC8-467E-93D7-CE1BA44B51C5}">
   <dimension ref="A1:F54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
         <v>40</v>
@@ -1681,8 +1678,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
         <v>45</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1701,8 +1698,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
         <v>46</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1721,8 +1718,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
         <v>47</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1741,8 +1738,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
         <v>48</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -1761,8 +1758,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
         <v>49</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -1781,8 +1778,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
         <v>50</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -1801,8 +1798,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
         <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -1821,8 +1818,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="13" t="s">
         <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -1841,8 +1838,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
         <v>66</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -1861,8 +1858,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
         <v>53</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -1881,8 +1878,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
         <v>54</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -1901,7 +1898,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>55</v>
       </c>
@@ -1921,7 +1918,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>56</v>
       </c>
@@ -1941,7 +1938,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>57</v>
       </c>
@@ -1961,7 +1958,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>58</v>
       </c>
@@ -1981,7 +1978,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>59</v>
       </c>
@@ -2001,7 +1998,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>67</v>
       </c>
@@ -2021,7 +2018,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>60</v>
       </c>
@@ -2041,7 +2038,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>61</v>
       </c>
@@ -2061,7 +2058,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>62</v>
       </c>
@@ -2081,7 +2078,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>63</v>
       </c>
@@ -2101,7 +2098,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>64</v>
       </c>
@@ -2121,7 +2118,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>65</v>
       </c>
@@ -2141,7 +2138,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>68</v>
       </c>
@@ -2161,7 +2158,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>69</v>
       </c>
@@ -2181,7 +2178,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>70</v>
       </c>
@@ -2201,7 +2198,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>71</v>
       </c>
@@ -2221,7 +2218,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>83</v>
       </c>
@@ -2241,7 +2238,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>72</v>
       </c>
@@ -2261,7 +2258,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>73</v>
       </c>
@@ -2281,7 +2278,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>74</v>
       </c>
@@ -2301,7 +2298,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>75</v>
       </c>
@@ -2321,7 +2318,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>76</v>
       </c>
@@ -2341,7 +2338,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>77</v>
       </c>
@@ -2361,7 +2358,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>78</v>
       </c>
@@ -2381,7 +2378,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>79</v>
       </c>
@@ -2401,7 +2398,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>80</v>
       </c>
@@ -2421,7 +2418,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>81</v>
       </c>
@@ -2441,7 +2438,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>82</v>
       </c>
@@ -2461,7 +2458,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>90</v>
       </c>
@@ -2481,7 +2478,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>84</v>
       </c>
@@ -2501,7 +2498,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>85</v>
       </c>
@@ -2521,7 +2518,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>86</v>
       </c>
@@ -2541,7 +2538,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>87</v>
       </c>
@@ -2561,7 +2558,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>88</v>
       </c>
@@ -2581,7 +2578,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>89</v>
       </c>
@@ -2601,7 +2598,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>91</v>
       </c>
@@ -2621,7 +2618,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>92</v>
       </c>
@@ -2641,7 +2638,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>93</v>
       </c>
@@ -2661,7 +2658,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>97</v>
       </c>
@@ -2681,7 +2678,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>98</v>
       </c>
@@ -2701,7 +2698,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>100</v>
       </c>
@@ -2711,15 +2708,15 @@
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="11" t="s">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="B54" s="12"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="13"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Список проверенных переводов.xlsx
+++ b/Список проверенных переводов.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Disposable\Desktop\СЦЕНАРИИ\В процессе\DanilChem\DBD_Localization\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/842728658d9fcf8d/Рабочий стол/СЦЕНАРИИ/Незакончено/DBD_Trans-master/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71C612B6-6801-4F16-ACDA-EF5E9A566EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{71C612B6-6801-4F16-ACDA-EF5E9A566EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA6CE23A-25CB-453E-8E09-BF363105D0B9}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Маньяки" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -770,13 +773,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="5" t="s">
         <v>40</v>
@@ -794,7 +797,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -814,7 +817,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
@@ -834,7 +837,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
@@ -854,7 +857,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>3</v>
       </c>
@@ -874,7 +877,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>4</v>
       </c>
@@ -894,7 +897,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>5</v>
       </c>
@@ -914,7 +917,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>6</v>
       </c>
@@ -934,7 +937,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>94</v>
       </c>
@@ -954,7 +957,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>7</v>
       </c>
@@ -974,7 +977,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>8</v>
       </c>
@@ -994,7 +997,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>9</v>
       </c>
@@ -1014,7 +1017,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>10</v>
       </c>
@@ -1034,7 +1037,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>11</v>
       </c>
@@ -1054,7 +1057,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>12</v>
       </c>
@@ -1074,7 +1077,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>13</v>
       </c>
@@ -1094,7 +1097,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>14</v>
       </c>
@@ -1114,7 +1117,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>15</v>
       </c>
@@ -1134,7 +1137,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>16</v>
       </c>
@@ -1154,7 +1157,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>17</v>
       </c>
@@ -1175,7 +1178,7 @@
       </c>
       <c r="H20" s="8"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
         <v>18</v>
       </c>
@@ -1195,7 +1198,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>19</v>
       </c>
@@ -1215,7 +1218,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>20</v>
       </c>
@@ -1235,7 +1238,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>21</v>
       </c>
@@ -1255,7 +1258,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>22</v>
       </c>
@@ -1275,7 +1278,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>23</v>
       </c>
@@ -1295,7 +1298,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>24</v>
       </c>
@@ -1315,7 +1318,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>25</v>
       </c>
@@ -1335,7 +1338,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>26</v>
       </c>
@@ -1355,7 +1358,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>27</v>
       </c>
@@ -1375,7 +1378,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
         <v>28</v>
       </c>
@@ -1395,7 +1398,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>29</v>
       </c>
@@ -1415,7 +1418,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>30</v>
       </c>
@@ -1435,7 +1438,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>31</v>
       </c>
@@ -1455,7 +1458,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>32</v>
       </c>
@@ -1475,7 +1478,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>33</v>
       </c>
@@ -1495,7 +1498,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>34</v>
       </c>
@@ -1515,7 +1518,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>35</v>
       </c>
@@ -1535,7 +1538,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
         <v>36</v>
       </c>
@@ -1555,7 +1558,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
         <v>37</v>
       </c>
@@ -1575,7 +1578,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
         <v>38</v>
       </c>
@@ -1595,7 +1598,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
         <v>39</v>
       </c>
@@ -1615,7 +1618,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
         <v>96</v>
       </c>
@@ -1635,7 +1638,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>102</v>
       </c>
@@ -1654,13 +1657,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F14EA754-DAC8-467E-93D7-CE1BA44B51C5}">
   <dimension ref="A1:F54"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
         <v>40</v>
@@ -1678,7 +1681,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>45</v>
       </c>
@@ -1698,7 +1701,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>46</v>
       </c>
@@ -1718,7 +1721,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>47</v>
       </c>
@@ -1738,7 +1741,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>48</v>
       </c>
@@ -1758,7 +1761,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>49</v>
       </c>
@@ -1778,7 +1781,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>50</v>
       </c>
@@ -1798,7 +1801,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>51</v>
       </c>
@@ -1818,7 +1821,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>52</v>
       </c>
@@ -1838,7 +1841,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>66</v>
       </c>
@@ -1858,7 +1861,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>53</v>
       </c>
@@ -1878,7 +1881,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>54</v>
       </c>
@@ -1898,8 +1901,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
         <v>55</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -1918,8 +1921,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>56</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -1938,8 +1941,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
         <v>57</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -1958,7 +1961,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>58</v>
       </c>
@@ -1978,7 +1981,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>59</v>
       </c>
@@ -1998,7 +2001,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>67</v>
       </c>
@@ -2018,7 +2021,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>60</v>
       </c>
@@ -2038,7 +2041,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>61</v>
       </c>
@@ -2058,7 +2061,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>62</v>
       </c>
@@ -2078,7 +2081,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>63</v>
       </c>
@@ -2098,7 +2101,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>64</v>
       </c>
@@ -2118,7 +2121,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>65</v>
       </c>
@@ -2138,7 +2141,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>68</v>
       </c>
@@ -2158,7 +2161,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>69</v>
       </c>
@@ -2178,7 +2181,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>70</v>
       </c>
@@ -2198,7 +2201,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>71</v>
       </c>
@@ -2218,7 +2221,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>83</v>
       </c>
@@ -2238,7 +2241,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>72</v>
       </c>
@@ -2258,7 +2261,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>73</v>
       </c>
@@ -2278,7 +2281,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>74</v>
       </c>
@@ -2298,7 +2301,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>75</v>
       </c>
@@ -2318,7 +2321,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>76</v>
       </c>
@@ -2338,7 +2341,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>77</v>
       </c>
@@ -2358,7 +2361,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>78</v>
       </c>
@@ -2378,7 +2381,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>79</v>
       </c>
@@ -2398,7 +2401,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>80</v>
       </c>
@@ -2418,7 +2421,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>81</v>
       </c>
@@ -2438,7 +2441,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>82</v>
       </c>
@@ -2458,7 +2461,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>90</v>
       </c>
@@ -2478,7 +2481,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>84</v>
       </c>
@@ -2498,7 +2501,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>85</v>
       </c>
@@ -2518,7 +2521,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>86</v>
       </c>
@@ -2538,7 +2541,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>87</v>
       </c>
@@ -2558,7 +2561,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>88</v>
       </c>
@@ -2578,7 +2581,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>89</v>
       </c>
@@ -2598,7 +2601,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>91</v>
       </c>
@@ -2618,7 +2621,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>92</v>
       </c>
@@ -2638,7 +2641,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>93</v>
       </c>
@@ -2658,7 +2661,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>97</v>
       </c>
@@ -2678,7 +2681,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>98</v>
       </c>
@@ -2698,7 +2701,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>100</v>
       </c>
@@ -2708,7 +2711,7 @@
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
         <v>103</v>
       </c>
@@ -2720,5 +2723,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Список проверенных переводов.xlsx
+++ b/Список проверенных переводов.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/842728658d9fcf8d/Рабочий стол/СЦЕНАРИИ/Незакончено/DBD_Trans-master/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Disposable\Desktop\СЦЕНАРИИ\В процессе\DanilChem\DBD_Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{71C612B6-6801-4F16-ACDA-EF5E9A566EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA6CE23A-25CB-453E-8E09-BF363105D0B9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6FD795-5EC2-446F-A589-B3B4B46B9123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Маньяки" sheetId="1" r:id="rId1"/>
@@ -20,9 +20,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -773,13 +770,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="5" t="s">
         <v>40</v>
@@ -797,7 +794,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -817,7 +814,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
@@ -837,7 +834,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
@@ -857,7 +854,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>3</v>
       </c>
@@ -877,7 +874,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>4</v>
       </c>
@@ -897,7 +894,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>5</v>
       </c>
@@ -917,7 +914,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>6</v>
       </c>
@@ -937,7 +934,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>94</v>
       </c>
@@ -957,7 +954,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>7</v>
       </c>
@@ -977,7 +974,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>8</v>
       </c>
@@ -997,7 +994,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>9</v>
       </c>
@@ -1017,7 +1014,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>10</v>
       </c>
@@ -1037,7 +1034,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>11</v>
       </c>
@@ -1057,7 +1054,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
         <v>12</v>
       </c>
@@ -1077,7 +1074,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
         <v>13</v>
       </c>
@@ -1097,7 +1094,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>14</v>
       </c>
@@ -1117,7 +1114,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>15</v>
       </c>
@@ -1137,7 +1134,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
         <v>16</v>
       </c>
@@ -1157,7 +1154,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>17</v>
       </c>
@@ -1178,7 +1175,7 @@
       </c>
       <c r="H20" s="8"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
         <v>18</v>
       </c>
@@ -1198,7 +1195,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>19</v>
       </c>
@@ -1218,7 +1215,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
         <v>20</v>
       </c>
@@ -1238,7 +1235,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>21</v>
       </c>
@@ -1258,7 +1255,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>22</v>
       </c>
@@ -1278,7 +1275,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>23</v>
       </c>
@@ -1298,7 +1295,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>24</v>
       </c>
@@ -1318,7 +1315,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>25</v>
       </c>
@@ -1338,7 +1335,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>26</v>
       </c>
@@ -1358,7 +1355,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>27</v>
       </c>
@@ -1378,7 +1375,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
         <v>28</v>
       </c>
@@ -1398,7 +1395,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>29</v>
       </c>
@@ -1418,7 +1415,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
         <v>30</v>
       </c>
@@ -1438,7 +1435,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>31</v>
       </c>
@@ -1458,7 +1455,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
         <v>32</v>
       </c>
@@ -1478,7 +1475,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>33</v>
       </c>
@@ -1498,7 +1495,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>34</v>
       </c>
@@ -1518,7 +1515,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>35</v>
       </c>
@@ -1538,7 +1535,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
         <v>36</v>
       </c>
@@ -1558,7 +1555,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
         <v>37</v>
       </c>
@@ -1578,7 +1575,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
         <v>38</v>
       </c>
@@ -1598,7 +1595,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
         <v>39</v>
       </c>
@@ -1618,7 +1615,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
         <v>96</v>
       </c>
@@ -1638,7 +1635,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>102</v>
       </c>
@@ -1657,13 +1654,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F14EA754-DAC8-467E-93D7-CE1BA44B51C5}">
   <dimension ref="A1:F54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
         <v>40</v>
@@ -1681,7 +1678,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>45</v>
       </c>
@@ -1701,7 +1698,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>46</v>
       </c>
@@ -1721,7 +1718,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>47</v>
       </c>
@@ -1741,7 +1738,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>48</v>
       </c>
@@ -1761,7 +1758,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>49</v>
       </c>
@@ -1781,7 +1778,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>50</v>
       </c>
@@ -1801,7 +1798,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>51</v>
       </c>
@@ -1821,7 +1818,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>52</v>
       </c>
@@ -1841,7 +1838,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>66</v>
       </c>
@@ -1861,7 +1858,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>53</v>
       </c>
@@ -1881,7 +1878,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>54</v>
       </c>
@@ -1901,7 +1898,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>55</v>
       </c>
@@ -1921,7 +1918,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>56</v>
       </c>
@@ -1941,7 +1938,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>57</v>
       </c>
@@ -1961,8 +1958,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="s">
         <v>58</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -1981,8 +1978,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="13" t="s">
         <v>59</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -2001,8 +1998,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="13" t="s">
         <v>67</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -2021,8 +2018,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="13" t="s">
         <v>60</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -2041,8 +2038,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="13" t="s">
         <v>61</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -2061,8 +2058,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="13" t="s">
         <v>62</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -2081,8 +2078,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="13" t="s">
         <v>63</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -2101,8 +2098,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="13" t="s">
         <v>64</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -2121,8 +2118,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="13" t="s">
         <v>65</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -2141,7 +2138,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>68</v>
       </c>
@@ -2161,7 +2158,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>69</v>
       </c>
@@ -2181,7 +2178,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>70</v>
       </c>
@@ -2201,7 +2198,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>71</v>
       </c>
@@ -2221,7 +2218,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>83</v>
       </c>
@@ -2241,7 +2238,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>72</v>
       </c>
@@ -2261,7 +2258,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>73</v>
       </c>
@@ -2281,7 +2278,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>74</v>
       </c>
@@ -2301,7 +2298,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>75</v>
       </c>
@@ -2321,7 +2318,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>76</v>
       </c>
@@ -2341,7 +2338,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>77</v>
       </c>
@@ -2361,7 +2358,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>78</v>
       </c>
@@ -2381,7 +2378,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>79</v>
       </c>
@@ -2401,7 +2398,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>80</v>
       </c>
@@ -2421,7 +2418,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>81</v>
       </c>
@@ -2441,7 +2438,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>82</v>
       </c>
@@ -2461,7 +2458,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>90</v>
       </c>
@@ -2481,7 +2478,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>84</v>
       </c>
@@ -2501,7 +2498,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>85</v>
       </c>
@@ -2521,7 +2518,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>86</v>
       </c>
@@ -2541,7 +2538,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>87</v>
       </c>
@@ -2561,7 +2558,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>88</v>
       </c>
@@ -2581,7 +2578,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>89</v>
       </c>
@@ -2601,7 +2598,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>91</v>
       </c>
@@ -2621,7 +2618,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>92</v>
       </c>
@@ -2641,7 +2638,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>93</v>
       </c>
@@ -2661,7 +2658,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>97</v>
       </c>
@@ -2681,7 +2678,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>98</v>
       </c>
@@ -2701,7 +2698,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>100</v>
       </c>
@@ -2711,7 +2708,7 @@
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="10" t="s">
         <v>103</v>
       </c>

--- a/Список проверенных переводов.xlsx
+++ b/Список проверенных переводов.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Disposable\Desktop\СЦЕНАРИИ\В процессе\DanilChem\DBD_Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6FD795-5EC2-446F-A589-B3B4B46B9123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB136566-3F14-46A5-897C-CD7E15AEECE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2139,7 +2139,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="13" t="s">
         <v>68</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -2159,7 +2159,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="13" t="s">
         <v>69</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -2179,7 +2179,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="13" t="s">
         <v>70</v>
       </c>
       <c r="B27" s="2" t="s">
@@ -2199,7 +2199,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="13" t="s">
         <v>71</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -2299,7 +2299,7 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="13" t="s">
         <v>75</v>
       </c>
       <c r="B33" s="2" t="s">
@@ -2319,7 +2319,7 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="13" t="s">
         <v>76</v>
       </c>
       <c r="B34" s="2" t="s">

--- a/Список проверенных переводов.xlsx
+++ b/Список проверенных переводов.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Disposable\Desktop\СЦЕНАРИИ\В процессе\DanilChem\DBD_Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB136566-3F14-46A5-897C-CD7E15AEECE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A650B6-448B-413C-8723-DBDB379E5635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2219,7 +2219,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="13" t="s">
         <v>83</v>
       </c>
       <c r="B29" s="2" t="s">
@@ -2239,7 +2239,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="13" t="s">
         <v>72</v>
       </c>
       <c r="B30" s="2" t="s">
@@ -2259,7 +2259,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="13" t="s">
         <v>73</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -2339,7 +2339,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="13" t="s">
         <v>77</v>
       </c>
       <c r="B35" s="2" t="s">
@@ -2359,7 +2359,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="13" t="s">
         <v>78</v>
       </c>
       <c r="B36" s="2" t="s">
@@ -2379,7 +2379,7 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="13" t="s">
         <v>79</v>
       </c>
       <c r="B37" s="2" t="s">
@@ -2419,7 +2419,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="13" t="s">
         <v>81</v>
       </c>
       <c r="B39" s="2" t="s">
@@ -2439,7 +2439,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="13" t="s">
         <v>82</v>
       </c>
       <c r="B40" s="2" t="s">
@@ -2499,7 +2499,7 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="13" t="s">
         <v>85</v>
       </c>
       <c r="B43" s="2" t="s">
@@ -2519,7 +2519,7 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B44" s="2" t="s">
@@ -2539,7 +2539,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="13" t="s">
         <v>87</v>
       </c>
       <c r="B45" s="2" t="s">
@@ -2599,7 +2599,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="13" t="s">
         <v>91</v>
       </c>
       <c r="B48" s="2" t="s">
@@ -2619,7 +2619,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="13" t="s">
         <v>92</v>
       </c>
       <c r="B49" s="2" t="s">
@@ -2659,7 +2659,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="13" t="s">
         <v>97</v>
       </c>
       <c r="B51" s="2" t="s">
@@ -2679,7 +2679,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="13" t="s">
         <v>98</v>
       </c>
       <c r="B52" s="2" t="s">
